--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_003/extracted.xlsx
@@ -275,6 +275,11 @@
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1261,17 +1266,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Orion-B Liquid-Cooled Avionics Module CHT Model</t>
+          <t>Orion-B Avionics CHT Model</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict board-level hot spots and cold plate ΔT for fin geometry and TIM stackup design selection at 120–160 W total dissipation</t>
+          <t>Predict board-level hot spots and cold plate ΔT for liquid-cooled avionics module design go/no-go before EVT</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer (CHT) CFD model of a liquid-cooled avionics cold plate using Ansys Fluent 2023R2 coupled with Ansys Mechanical. The model predicts peak component case temperatures and cold plate outlet ΔT over a 1.5–2.5 L/min, 20–28 °C inlet, 100–160 W load envelope. Results support a design go/no-go decision before EVT: selection of straight vs. wavy microchannel fin geometry and TIM stackup, and pump setpoint sizing to keep worst-case component case temperature below 85 °C at 28 °C bay ambient.</t>
+          <t>Conjugate heat transfer (CHT) simulation of a liquid-cooled avionics module for the Orion-B rack, rejecting heat to a 50/50 ethylene glycol-water loop. The model predicts component case temperatures and cold plate ΔT at 120–160 W total dissipation to support fin geometry selection, TIM stackup selection, and pump setpoint sizing, with a hard requirement that worst-case component case temperature remains below 85 °C at 28 °C bay ambient.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1305,9 +1310,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1426,7 +1431,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Peak Component Case Temperature Limit</t>
+          <t>Worst-Case Component Case Temperature Limit</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1436,7 +1441,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Worst-case component case temperature must remain below 85 °C at 28 °C bay ambient across the 100–160 W load envelope; absolute margins reported as 2–6 °C depending on model assumptions.</t>
+          <t>Worst-case component case temperature must remain below 85 °C at 28 °C bay ambient across the 120–160 W total dissipation envelope; margin to limit is 2–6 °C depending on assumptions, making absolute accuracy critical for go/no-go decision before EVT.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1453,34 +1458,34 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Design Selection Support</t>
+          <t>Ansys Fluent 2023R2 CHT CFD Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Model must discriminate consistently between straight and wavy microchannel fin geometries and TIM stackup options to support go/no-go decision before EVT.</t>
+          <t>Pressure-based segregated RANS (k-ω SST) solver fully coupled with solid conduction via CHT for coolant flow and board-level thermal prediction in the Orion-B cold plate assembly.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R2 CHT Model</t>
+          <t>EVT Bench Correlation Dataset (EVT-CP-07 series)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Pressure-based segregated RANS (k-ω SST) solver for coolant flow coupled two-way with Ansys Mechanical solid conduction; covers Al 6061 cold plate, Cu spreaders, PCB stack, and 50/50 EGW coolant.</t>
+          <t>Experimental thermocouple, RTD, IR thermography, and flow meter measurements from the bench correlation test article used to validate the CHT model predictions at nominal conditions.</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1497,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>EVT Bench Correlation Dataset</t>
+          <t>Material Property Library (matlib_2023-05-02.json)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Bench measurements from chiller loop test: 10× K-type thermocouples, 2× RTDs on inlet/outlet, FLIR A655sc IR camera; flow 1.86–1.91 L/min, bay ambient 28±1 °C, run ID EVT-CP-07 and associated series.</t>
+          <t>Thermal and transport property data for Al 6061-T6, Cu, PCB stack, TIM, and 50/50 EGW used as model inputs; revised 05/02 from original 02/07 version, with some correlation runs predating the revision.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Material Properties Library</t>
+          <t>Fin Geometry and TIM Stackup Discrimination Requirement</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Thermal and transport properties for Al 6061-T6, Cu, PCB laminate (measured through-thickness), TIM pad, and 50/50 EGW (CoolProp); updated 05/02 from earlier 02/07 version.</t>
+          <t>The model must reliably rank straight vs. wavy microchannel fin geometries and TIM stackup configurations relative to each other so that a design selection can be made before EVT; qualitative ranking consistency across runs is a secondary acceptance criterion.</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1956,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study</t>
+          <t>Mesh Convergence Study (G1/G2/G3)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1966,12 +1971,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three fluid meshes (G1: 2.4M, G2: 6.8M, G3: 14.2M cells) exercised at Q=140 W, Tin=20 °C, 2.0 L/min. Peak case temperatures: G1=78.6 °C, G2=75.8 °C, G3=74.9 °C. G1→G2 change is 3.6%; G2→G3 change is 1.2% on peak temp and 1.4% on ΔTmax. Slide claims "&lt;1%" G2→G3 change, which is arithmetically inconsistent. Final production runs used G2 despite G3 showing non-negligible hotspot shift. Max skewness 0.92 flagged in solid mesh.</t>
+          <t>Three fluid-domain meshes (2.4M, 6.8M, 14.2M cells) run at Q=140 W, Tin=20 °C, 2.0 L/min to assess discretization sensitivity. Peak case temperatures were G1: 78.6 °C, G2: 75.8 °C, G3: 74.9 °C. G1→G2 change is 3.6%; G2→G3 change is 1.2% on peak and 1.4% on ΔTmax. Final design runs used G2 despite non-negligible G2→G3 shift; GCI not formally computed. Maximum skewness 0.92 flagged in solid mesh.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Successive grid refinement (Richardson-type comparison)</t>
+          <t>Self-convergence across three mesh refinement levels</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -1986,7 +1991,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>G2→G3 peak temp shift: 0.9 °C (1.2%); G1→G2 shift: 2.8 °C (3.6%)</t>
+          <t>G2→G3 peak temp change: 1.2%; G1→G2: 3.6%</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -1998,7 +2003,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Outlet Temperature Rise Comparison</t>
+          <t>Outlet Temperature Rise Comparison (Model vs. Test)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2008,12 +2013,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Predicted outlet temperature rise (model: 2.9 °C on G2) compared to bench measurement (test: 3.1–3.4 °C) at nominally matched conditions. Discrepancy is 0.2–0.5 °C (6–17%) on a global energy-balance metric.</t>
+          <t>Comparison of model-predicted coolant outlet temperature rise to bench measurements at nominally matched conditions. Model predicts 2.9 °C rise (G2); test measured 3.1–3.4 °C. Conditions were not fully matched: model used Tin=20.0 °C while test RTD recorded 23.1±0.3 °C for run EVT-CP-07; flow rate drifted 1.86–1.91 L/min in test vs. 2.0 L/min in model.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>EVT bench RTD outlet measurements (run ID EVT-CP-07 series)</t>
+          <t>EVT bench test RTD outlet measurements (EVT-CP-07 series)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2023,19 +2028,19 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Model 2.9 °C vs. test 3.1–3.4 °C; difference 0.2–0.5 °C</t>
+          <t>Model 2.9 °C vs. test 3.1–3.4 °C; offset 0.2–0.5 °C on ΔT</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Peak Case Temperature Comparison (Q1 Hot Spot)</t>
+          <t>Peak Component Case Temperature Comparison (Model vs. IR/TC)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2045,12 +2050,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Model predicted Q1 peak case 76–78 °C (grid-dependent); IR camera (FLIR A655sc, emissivity 0.92) measured 72–74 °C after emissivity tuning. Slide caption claims "within 2 K on critical nodes," but table footnote shows Q1 offset of 4.6–6.2 K when test Tin=23.1 °C is used as reference instead of the model's 20.0 °C. Inlet temperature mismatch (3.1 °C) is unresolved and directly inflates apparent model error.</t>
+          <t>Comparison of model-predicted peak case temperature (Q1) to IR thermography and thermocouple bench data. Model predicts 76–78 °C (grid-dependent); IR measures 72–74 °C after emissivity tuning (ε=0.92). Slide caption claims "within 2 K on critical nodes," but table footnote shows Q1 offset of 4.6–6.2 K when test Tin=23.1 °C is used as reference. Hotspot lateral location at Q2 underestimated by ~6 mm.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>FLIR A655sc IR thermography and K-type thermocouple data (EVT bench)</t>
+          <t>FLIR A655sc IR thermography and K-type thermocouple board measurements</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2060,7 +2065,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Apparent offset 4–4 °C (caption) to 4.6–6.2 °C (footnote with correct Tin reference)</t>
+          <t>Peak case offset: 2–4 K (claim) to 4.6–6.2 K (footnote corrected for Tin); hotspot position error ~6 mm</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2072,7 +2077,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>One-at-a-Time Sensitivity / DOE</t>
+          <t>One-at-a-Time Sensitivity / Partial Monte Carlo UQ</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2082,12 +2087,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>OAT sweeps on Tin (20–28 °C), flow rate (1.5–2.5 L/min), kTIM (2.4–5.0 W/m·K), board kzz (0.6–1.2 W/m·K). Peak temp sensitivities quantified. A claimed 200-sample Monte Carlo with LHS is documented but only 20 points plotted; seeds and PDFs not archived. Final uncertainty band ±2 °C stated without decomposition into contributions.</t>
+          <t>DOE sweeps on Tin, flow rate, kTIM, and board kzz characterizing peak temperature sensitivity. Header claims 200-sample LHS Monte Carlo but only 20 points plotted; seeds and PDFs not archived. Final uncertainty band reported as ±2 °C total without decomposition into contributions. Earlier draft allocated ±1.5 °C to inlet temperature alone, suggesting the aggregated band is underestimated or inconsistently derived.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>N/A (parametric sweep, no experimental comparator)</t>
+          <t>Parametric sensitivity bounds vs. 85 °C specification limit</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2097,12 +2102,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>One-at-a-time parametric sweep; claimed LHS Monte Carlo (incomplete)</t>
+          <t>One-at-a-time DOE; partial Monte Carlo (LHS, 20 points used)</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>±2 °C total uncertainty (undecomposed); kTIM contributes +2.8 °C across plausible range</t>
+          <t>±2 °C total uncertainty (undecomposed); peak sensitivity −3.2 °C per 0.5 L/min; +2.8 °C across kTIM range</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2256,12 +2261,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented release quality process; version-controlled inputs; reproducible runs</t>
+          <t>Commercial solver with documented version, regression testing, and change-control evidence for all model inputs used in final runs.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R2 HF2 is a well-known commercial solver with vendor QA processes (implied but not cited explicitly). Journal files are archived. However, two manual boundary-relabeling steps are noted, threatening reproducibility. Material library was updated mid-project (02/07 → 05/02) and some correlation runs predate the update. CAD rev B fin geometry was not propagated into the G2 mesh used for final runs (mismatch acknowledged). No independent replication performed. Evidence is partial and contains documented integrity gaps.</t>
+          <t>Fluent 2023R2 HF2 and Mechanical 2023R1 are identified (Slide 11). Material library versioning exists (matlib files dated 02/07 and 05/02), but some correlation runs predate the 05/02 update, creating configuration traceability gaps. CAD rev B fin fillet change was not propagated to the G2 mesh used for final runs (mesh built on rev A). Journal files are archived but two manual boundary-relabeling steps are noted that could affect reproducibility. No regression test suite or ISO QMS evidence cited.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2290,12 +2295,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Basic demonstration that solver correctly solves governing equations for CHT problems; reference to benchmark or analytical solution</t>
+          <t>Solver correctly implements governing equations, evidenced by benchmark or analytical solution comparison.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>No benchmark comparison, manufactured solution, or independent CHT validation case is cited in the report. Ansys Fluent's lineage provides implicit code verification, but no project-specific evidence is presented. Turbulence model selection (k-ω SST) is stated without reference to validation studies for microchannel internal flow. Level kept at 2 reflecting reliance on commercial solver reputation alone.</t>
+          <t>Fluent 2023R2 is a widely validated commercial solver with implicit benchmark verification through Ansys's published verification manuals. No project-specific benchmark comparison (e.g., Nusselt number correlation for rectangular microchannels, analytical conduction solution) was documented in this report. Reliance is on vendor credibility of the commercial code only.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2324,12 +2329,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with &lt;1% change between successive refinement levels on all QoIs; GCI or equivalent reported; production mesh selected on converged level</t>
+          <t>Mesh convergence demonstrated with GCI &lt; 1% on QoI (peak case temperature and ΔT) or Richardson extrapolation to grid-independent value; final mesh selection justified against converged solution.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three meshes run (G1–G3). G2→G3 peak temp shift is 1.2% (not &lt;1% as claimed) and ΔTmax shift is 1.4%. Production runs used G2 rather than the finest mesh G3. Solid mesh has max skewness 0.92 (flagged in solver log). No GCI or Richardson extrapolation computed. CAD rev mismatch between G2 mesh and actual rev B geometry further undermines discretization confidence. Evidence is present but falls short of convergence criterion.</t>
+          <t>Three meshes were run (G1: 2.4M, G2: 6.8M, G3: 14.2M cells) and peak temperatures reported (Slide 5). G1→G2 shift is 3.6% and G2→G3 is 1.2–1.4% on the primary QoI. GCI was not formally computed and Richardson extrapolation was not performed. Final runs used G2 rather than G3 to meet walltime constraints, despite G3 showing a non-negligible shift. Solid mesh max skewness 0.92 flagged but not assessed for impact. No temporal discretization study reported (steady-state).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2351,19 +2356,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals to tight targets; mass imbalance checked; energy convergence confirmed</t>
+          <t>Residuals and mass imbalance converge to defined targets; energy residual meets tighter criterion appropriate for thermal QoI.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals driven to 1e-5 (momentum/continuity) and 1e-8 (energy); SIMPLEC with pseudo-transient (0.5 s); under-relaxation 0.5 on thermal coupling; mass imbalance &lt;0.2%. These are well-documented and meet typical CHT practice. One concern is that a 50 s transient run was repurposed as steady-state for reporting, which is an ambiguity in the convergence record but does not indicate solver divergence.</t>
+          <t>Solver convergence targets are documented: momentum/continuity residuals to 1e-5, energy to 1e-8, mass imbalance &lt;0.2% (Slide 4). SIMPLEC with pseudo-transient enabled; under-relaxation 0.5 on thermal coupling. These are reasonable and explicitly stated targets for a CHT problem. Convergence monitoring was performed.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2392,12 +2397,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of boundary conditions, mesh quality, and material assignments; documented setup checklist signed off</t>
+          <t>Independent review of boundary conditions, mesh quality, and post-processing; model setup checklist completed and signed off.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>An internal peer check against a setup checklist was performed on 04/28, but no independent replication was done due to schedule. Several setup errors are documented: inlet temperature mismatch (model 20 °C vs. test 23.1 °C for same run ID EVT-CP-07), adiabatic side panels while test had free convection, TIM property mismatch (kTIM=5.0 assumed vs. 2.4–3.1 measured at assembly pressure), cover pad conduction path omitted, and CAD rev A mesh used with rev B design. These are substantive use errors that partially survive into the correlation comparison.</t>
+          <t>An internal peer check on the setup checklist was completed 04/28 (Slide 11). However, no independent replication was performed due to schedule. Boundary condition errors were identified post-hoc (Tin=20 °C in model vs. 23.1 °C in test for run EVT-CP-07; Slide 7/9). CAD/mesh mismatch (rev A mesh for rev B geometry) was acknowledged but not corrected before final runs. Analyst's first time on full CHT/EGW workflow noted. Manual boundary-relabeling steps reduce reproducibility confidence.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2426,12 +2431,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations justified for the flow regime; turbulence model selection supported by microchannel-relevant validation literature; known simplifications documented with sensitivity</t>
+          <t>Governing equations and turbulence model selection justified for the flow regime; known limitations documented with impact assessment; radiation and contact resistance treatment justified.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>RANS k-ω SST with automatic wall treatment is stated but the conflicting y+ guidance (low-Re intent vs. "enhanced wall functions acceptable for y+ 30–100") is unresolved and the achieved y+ of 5–60 on baseline mesh does not meet the original low-Re criterion. Radiation is neglected in the baseline but a sensitivity shows 1.3 °C effect. Graphite isotropy assumption, PCB homogenization, and TIM "perfect contact" baseline are documented simplifications. Physics scope is reasonable for internal forced convection CHT, but the wall treatment inconsistency and the un-archived radiation model state reduce confidence.</t>
+          <t>k-ω SST RANS with CHT is an appropriate model class for internal microchannel cooling (Slide 4). However, contradictory wall treatment intent is documented: low-Re intent (y+&lt;1) vs. enhanced wall functions acceptable at y+~30–100, with measured y+ 5–60 on baseline grid. Radiation was neglected in baseline then added inconsistently in sensitivity (side panels remained adiabatic). TIM was modeled as uniform 5.0 W/m-K when vendor data indicates 2.4–3.1 W/m-K at relevant pressures. Graphite spreader isotropic approximation acknowledged. PCB homogenization used without uncertainty assessment. Known limitations are documented in Slide 12 but no quantitative impact assessment of model form errors is provided.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2460,12 +2465,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from traceable measurements or certified sources; boundary conditions from calibrated measurements; input uncertainties characterized</t>
+          <t>Material properties from test data or authoritative sources; boundary conditions matched to hardware; input uncertainties characterized.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>PCB through-thickness conductivity was measured (0.9 W/m·K at 25 °C). Al 6061 and Cu from ASM data. EGW properties from CoolProp (one correlation run referenced "water at 25 °C"). TIM conductivity assumed at 5.0 W/m·K in main runs; vendor sheet shows 2.4–3.1 W/m·K at relevant assembly pressures; phase-change film (not pad) specified for Q1/Q2 per BOM, creating a material identity conflict. Load input is 120 W constant while electrical notebook specifies 135 W with ±15% duty cycling on Q1. Inlet temperature is documented with a 3.1 °C discrepancy between model and test for the same run. Input uncertainty characterization is partial (OAT sweeps exist) but not formally propagated.</t>
+          <t>Metals from ASM data; PCB through-thickness k measured at 25 °C (Slide 6). TIM conductivity from vendor sheet but nominal model value (5.0 W/m-K) is inconsistent with vendor-measured 2.4–3.1 W/m-K at actual assembly pressures; BOM discrepancy (pad vs. phase-change film on Q1/Q2) not resolved. EGW properties from CoolProp but one correlation deck references "water at 25 °C." Heat loads used 120 W constant while electrical notebook documents 135 W high-mode with ±15% duty cycle on Q1 (Slide 7). Inlet temperature mismatch between model (20.0 °C) and test (23.1±0.3 °C) for the same run ID. Flow rate not matched (model 2.0 L/min; test 1.86–1.91 L/min). Multiple input discrepancies reduce confidence.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2494,12 +2499,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article described; production-representative; sufficient to support comparison</t>
+          <t>Test article is production-representative; number of test articles and any unit-to-unit variability documented.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single bench test article is described (EVT-CP-07 series). Production representativeness is not explicitly confirmed. Mounting uses a silicone pad under the top cover (not in model) that introduces an extra conduction path. No multiple articles or statistical characterization of specimen variation are documented. For a pre-EVT design-decision use case, a single article is minimally acceptable.</t>
+          <t>A single bench test article was used for correlation (Slide 8). The article is described as an EVT unit with the target cold plate, board, and TIM stack. A silicone pad under the top cover (not in model) was noted as a difference. No information on number of test articles, unit-to-unit variability, or production representativeness assessment is provided. Single-unit characterization is typical for pre-EVT feasibility but limits statistical confidence.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2528,12 +2533,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation with stated uncertainty; controlled and stable flow and thermal conditions; test standard or protocol referenced</t>
+          <t>Calibrated instruments with documented uncertainty; controlled and logged environmental and flow conditions; test procedure follows recognized standard.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Instrumentation includes calibrated K-type thermocouples (×10), RTDs (×2), Coriolis meter, and FLIR A655sc (emissivity 0.92). Bay ambient 28±1 °C is documented. However, flow rate drifted 1.86–1.91 L/min during the 30-min dwell of the first series (target 2.0 L/min), and a later slide reports "2.0 L/min flat" without the drift band — an internal inconsistency. Inlet RTD logged 23.1±0.3 °C while the correlation slide labels it 20.0 °C. Thermocouple calibration uncertainty and IR uncertainty are not formally stated. No ASTM or ISO test standard referenced.</t>
+          <t>Instrumentation described: 10× K-type TCs, 2× RTDs, Coriolis flow meter, FLIR A655sc IR (Slide 8). Bay ambient 28±1 °C. Inlet RTD logged 23.1±0.3 °C. However, flow rate drifted 1.86–1.91 L/min over 30 min in first test series; a later slide reports "2.0 L/min flat" without the drift band, indicating inconsistent reporting. Instrument calibration status and measurement uncertainty budgets are not formally documented. No reference to ASTM, MIL, or other test standard. Silicone pad mounting fixture introduces an uncharacterized conduction path.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2562,12 +2567,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions demonstrably match experimental conditions within stated measurement uncertainties; any residual mismatch quantified and propagated</t>
+          <t>Model boundary conditions explicitly matched to measured test conditions for all comparison runs; differences quantified and propagated to output uncertainty.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>There are multiple documented and unresolved mismatches between model inputs and test conditions for the correlation run (EVT-CP-07): Tin 20.0 °C (model) vs. 23.1±0.3 °C (test); flow 2.0 L/min (model) vs. 1.86–1.91 L/min (test); side panels adiabatic (model) vs. free convection present (test); silicone cover pad present in test, absent in model; total load 120 W (model) vs. up to 135 W (electrical notebook). These mismatches directly degrade the validity of the comparison. A 6 W/m²·K external convection was added "ad hoc" after initial comparison but not propagated to all reported results. No formal input equivalency table or uncertainty propagation is presented.</t>
+          <t>Significant mismatches between model inputs and test conditions are explicitly documented but not corrected for the primary comparison. Tin: model 20.0 °C vs. test 23.1±0.3 °C for run EVT-CP-07 (Slide 7/9). Flow: model 2.0 L/min vs. test 1.86–1.91 L/min (Slide 8). Heat load: model 120 W vs. electrical notebook 135 W high-mode (Slide 7). These differences are acknowledged but no systematic re-run with matched inputs or uncertainty propagation of the mismatch to predicted temperatures is performed. The 3.1 °C Tin difference alone is estimated to affect peak temperature by ~1.7 °C (from sensitivity data), which is material relative to the 4.6–6.2 K discrepancy reported.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2596,12 +2601,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model vs. test on primary QoIs with uncertainty bands; multiple comparison points; statistical metrics</t>
+          <t>Quantitative comparison of model predictions to measurements on primary QoIs (peak case temperature, outlet ΔT) with uncertainty bands; discrepancies explained.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparisons are provided for outlet ΔT (model 2.9 °C vs. test 3.1–3.4 °C) and peak case temperature Q1 (model 76–78 °C vs. IR 72–74 °C). However, the caption claim "within 2 K" is contradicted by the footnote showing 4.6–6.2 K offset when the correct test Tin is used. Hotspot lateral spread at Q2 is underestimated by ~6 mm. Comparison points are limited (one operating condition). Uncertainty bands (±2 °C total) are stated but not decomposed. No correlation coefficient, RMS error across multiple nodes, or statistical validation metric is computed. Evidence is present but internally inconsistent and not statistically rigorous.</t>
+          <t>Outlet ΔT compared: model 2.9 °C vs. test 3.1–3.4 °C (Slide 9). Peak case (Q1): model 76–78 °C vs. IR 72–74 °C; offset 4.6–6.2 K when corrected for Tin mismatch (Slide 9). Hotspot location error ~6 mm at Q2. Slide caption claims "within 2 K" but footnote contradicts this at corrected reference. No formal validation metric (e.g., ASME V&amp;V 20 validation comparison metric u_val, E/u_val ratio) computed. Uncertainty bands on predictions not formally decomposed. Ranking of fin concepts reported as consistent across grids, which partially supports the relative-comparison use case.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2630,12 +2635,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model outputs (peak case temp, cold plate ΔT) directly address the safety and design decision criteria (85 °C limit, fin concept ranking)</t>
+          <t>QoIs (peak component case temperature, cold plate ΔT) are directly linked to the 85 °C specification and are measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The primary QoIs — peak component case temperature and cold plate outlet ΔT — directly map to the 85 °C design limit and pump sizing decision. Both are measurable computationally (nodal temperature, integrated energy) and experimentally (IR thermography, RTD). Fin concept ranking is reported as consistent across all runs, which is the key discriminating output for the design decision. The QoIs are appropriate and well-defined for the COU.</t>
+          <t>Peak component case temperature and coolant outlet ΔT are the directly regulated QoIs tied to the 85 °C specification limit and pump sizing decision (Slides 1, 9). Both are computed by the CHT model and measured in the bench test (IR thermography, RTDs, TCs). The fin geometry ranking decision is also supported by relative QoI comparisons. QoIs are well-defined and appropriate for the COU.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2664,12 +2669,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conducted at conditions spanning the COU envelope (1.5–2.5 L/min, 20–28 °C Tin, 100–160 W); geometry and TIM configuration match production intent</t>
+          <t>Validation test conditions (flow range, inlet temperature, heat load, geometry) span or bound the intended COU envelope; gaps explicitly identified and their impact on extrapolation assessed.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation was performed at a single nominal operating point (~20–23 °C, ~120–135 W, ~1.86–2.0 L/min) rather than spanning the full COU envelope (1.5–2.5 L/min, 20–28 °C, 100–160 W). The fin geometry in the test article corresponds to CAD rev A while the design decision involves rev B. TIM material in the test (pad) may differ from the BOM specification for Q1/Q2 (phase-change film). External convection present in bench but not consistently modeled. The OAT sensitivity sweeps partially address envelope coverage computationally but are not validated across the full range. Coverage of the COU is partial.</t>
+          <t>The COU envelope is 1.5–2.5 L/min, Tin 20–28 °C, 100–160 W (Slide 12). Validation was performed at a single nominal point (~2.0 L/min, ~20–23 °C, 120–135 W) with significant input condition mismatches. The test geometry used CAD rev A while final design uses rev B. External convection in the test was not modeled in the correlation baseline. No validation was performed at the envelope extremes (1.5 L/min, 28 °C, 160 W) where the 85 °C margin is tightest. Known gaps are identified in Slide 12 with planned corrective actions, but the validation does not yet cover the full COU envelope and extrapolation uncertainty is unquantified.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2854,7 +2859,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The model is accepted for the limited purpose of ranking fin geometry concepts (straight vs. wavy microchannels) and identifying dominant thermal sensitivities before EVT, consistent with the finding that fin concept ranking is stable across all runs. It is NOT accepted for absolute margin verification against the 85 °C limit without addressing the following conditions: (1) re-run G3 mesh on CAD rev B with y+ &lt; 2 enforced uniformly; (2) resolve TIM material identity (pad vs. phase-change film) and use vendor-measured conductivity at assembly pressure; (3) align model inlet temperature and flow rate with RTD-logged test conditions for all correlation runs; (4) add external convection and cover pad conduction path; (5) replace the undecomposed ±2 °C uncertainty band with a budgeted, traceable UQ analysis (archive Monte Carlo seeds and PDFs); (6) re-evaluate outlet ΔT and peak case temperature comparison after input equivalency is established. Absolute margins of 2–6 °C against the 85 °C spec are too narrow to accept the current model's quantitative predictions without resolving the identified input and setup discrepancies. The model in its current state should not be used as the sole basis for a go/no-go decision on thermal margin.</t>
+          <t>The CHT model is accepted for the limited purpose of ranking fin geometry concepts (straight vs. wavy microchannels) relative to each other before EVT, on the basis that qualitative ranking has been shown to be consistent across all grid levels and parametric variations. The model is NOT accepted for certifying absolute thermal margins to the 85 °C specification. Multiple significant deficiencies must be resolved before CDR use: (1) re-run on CAD rev B with G3 mesh enforcing y+&lt;2; (2) align model loads to 135 W high-mode electrical actuals; (3) match Tin to RTD-measured test value for all correlation comparisons; (4) resolve TIM property and BOM discrepancy (pad vs. phase-change film); (5) replace undecomposed ±2 °C band with a budgeted uncertainty analysis; (6) validate at COU envelope extremes (1.5 L/min, 28 °C, 160 W). Given the 2–6 °C margin to specification, the model in its current state is insufficient for absolute margin verification and must not be used as the sole basis for a thermal compliance sign-off.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
